--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-06-16T09:37:48.976Z</t>
+    <t>2026-06-16T10:25:24.971Z</t>
   </si>
   <si>
     <t>Westpac New Zealand - Helping New Zealanders with their banking.</t>
